--- a/assets/constructions/examples/ctd_tge_radial.xlsx
+++ b/assets/constructions/examples/ctd_tge_radial.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK6"/>
+  <dimension ref="A1:AO6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,50 +614,70 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QEED1616R17</t>
+          <t>QD-LFH1300-16A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>QE*DR/L</t>
+          <t>CoroCutⓇ QD shank tool for parting and grooving</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ZT02503</t>
+          <t>QD-04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>33.02</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ZTED02503-MG</t>
+          <t>CoroCut QD -size H (QD-NH-0400-0002-CM)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ISO_5610:16X16</t>
+          <t>ISO_5610:25.4X25.4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>DER_ZT0205W</t>
+          <t>COR_QD-040</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -665,10 +685,12 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>42</v>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -678,37 +700,33 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>16</v>
+        <v>25.4</v>
       </c>
       <c r="S2" t="n">
-        <v>16</v>
+        <v>25.4</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>125</v>
+        <v>152.4</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3</v>
-      </c>
+        <v>25.65</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr">
@@ -716,107 +734,105 @@
           <t>Steel</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>0.626</v>
+      </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2017/derek Металлорежущий инструмент и оснастка</t>
-        </is>
-      </c>
+          <t>2021/www.sandvik.coromant.com</t>
+        </is>
+      </c>
+      <c r="AL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QS-LF123L32C2525E</t>
+          <t>GPLC-125 019 20.20.C.1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CoroCutⓇ 1-2 QS shank tool for parting and grooving</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>123L2</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SANDVIK</t>
-        </is>
-      </c>
+          <t>PALBIT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CoroCut 2 -size L (N123L2-0800-0008-TF)</t>
+          <t>GP04...</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ISO_5610:25X25</t>
+          <t>ISO_5610:20X20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>COR_R123_L</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
+          <t>PALB_GP:04</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
-        <v>48.246</v>
-      </c>
-      <c r="N3" t="n">
-        <v>73.246</v>
-      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>132.246</v>
+        <v>125</v>
       </c>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4</v>
+      </c>
       <c r="AA3" t="n">
-        <v>25.5</v>
+        <v>20.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>2</v>
+      </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
         <v>2</v>
@@ -827,114 +843,124 @@
           <t>Steel</t>
         </is>
       </c>
-      <c r="AI3" t="n">
-        <v>0.522</v>
-      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
-        </is>
+          <t>2022/ palbit основной каталог.pdf</t>
+        </is>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>255.59</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AO3" t="n">
+        <v>23497.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WGCSML2525M0826C</t>
+          <t>QEFD2020R17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WGC</t>
+          <t>QE*DR/L</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>WID_WC/G..08</t>
+          <t>ZT0303</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>WC/G..08</t>
+          <t>ZTFD0303-MG</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ISO_5610:25X25</t>
+          <t>ISO_5610:20X20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>WIDIA_WGC:08</t>
+          <t>DER_ZT0303W</t>
         </is>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
       <c r="AA4" t="n">
-        <v>21.335</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>35.8</v>
-      </c>
+        <v>20.3</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="b">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
         <v>2</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr">
@@ -948,14 +974,28 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2020/ widia токарный инструмент</t>
-        </is>
+          <t>2017/derek Металлорежущий инструмент и оснастка</t>
+        </is>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AO4" t="n">
+        <v>3501.93</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QS-QD-RFE0800C10S</t>
+          <t>QS-RF123E17-1616B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -965,12 +1005,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CoroCutⓇ QD QS shank tool for parting and grooving</t>
+          <t>CoroCutⓇ 1-2 QS shank tool for parting and grooving</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>QD-02</t>
+          <t>123E2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -979,24 +1019,24 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>20.32</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n">
-        <v>40.64</v>
+        <v>34</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CoroCut QD -size E (QD-NE-0200-0002-CM)</t>
+          <t>CoroCut 2 -size E (N123E2-0200-0002-CM)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COR_QS_HP:15.785X15.875</t>
+          <t>COR_QS:16X16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>COR_QD-020</t>
+          <t>COR_R123_E</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -1005,7 +1045,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1013,16 +1053,16 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>15.875</v>
+        <v>16</v>
       </c>
       <c r="S5" t="n">
-        <v>15.875</v>
+        <v>16</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -1034,18 +1074,18 @@
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>15.875</v>
+        <v>16</v>
       </c>
       <c r="AB5" t="n">
-        <v>15.875</v>
+        <v>16</v>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr">
@@ -1054,7 +1094,7 @@
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>0.102</v>
+        <v>0.138</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
@@ -1064,11 +1104,17 @@
           <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WMTSL2525M116</t>
+          <t>WMTSR124044</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1083,7 +1129,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>WID_WMT..01</t>
+          <t>WID_WMT..04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1092,22 +1138,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>16.5</v>
+        <v>11.176</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>WMT..01</t>
+          <t>WMT..04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ISO_5610:25X25</t>
+          <t>ISO_5610:19.05X19.05</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>WIDIA_WMT:01</t>
+          <t>WIDIA_WMT:04</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -1120,7 +1166,7 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1130,30 +1176,30 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>25</v>
+        <v>19.05</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>19.05</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="W6" t="n">
-        <v>116.49</v>
+        <v>93.85299999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>1.5</v>
+        <v>3.962</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>3.962</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.5</v>
+        <v>3.962</v>
       </c>
       <c r="AA6" t="n">
-        <v>25</v>
+        <v>19.05</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="b">
@@ -1183,6 +1229,12 @@
           <t>2020/ widia токарный инструмент</t>
         </is>
       </c>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
